--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Encounter, Variation Outpatient (Visit)</t>
+    <t>This StructureDefinition contains the maps for VistA VISIT (file 9000010) to FHIR Encounter</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -249,10 +249,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t xml:space="preserve">Visit
@@ -653,13 +653,13 @@
     <t>CX.1 / EI.1</t>
   </si>
   <si>
+    <t>429: source value from VISIT - VISIT ID (#9000010-15001)</t>
+  </si>
+  <si>
     <t>Outpat.Visit.VisitIdentifier
 Outpat.Workload.VisitIdentifier</t>
   </si>
   <si>
-    <t>429: source value from VISIT - VISIT ID (#9000010-15001)</t>
-  </si>
-  <si>
     <t>Encounter.identifier.period</t>
   </si>
   <si>
@@ -737,13 +737,13 @@
     <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
   </si>
   <si>
+    <t>432: transform using finished on VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18) case not null, &lt; now</t>
+  </si>
+  <si>
     <t>Outpat.Visit.CheckOutDateTime
 Outpat.Workload.CheckOutDateTime</t>
   </si>
   <si>
-    <t>432: transform using finished on VISIT - CHECK OUT DATE&amp;TIME (#9000010-.18) case not null, &lt; now</t>
-  </si>
-  <si>
     <t>Encounter.statusHistory</t>
   </si>
   <si>
@@ -1009,13 +1009,13 @@
     <t>C*E.1</t>
   </si>
   <si>
+    <t>439: source value from VISIT - SERVICE CATEGORY (#9000010-.07)</t>
+  </si>
+  <si>
     <t>Outpat.Visit.ServiceCategory
 Outpat.Workload.ServiceCategory</t>
   </si>
   <si>
-    <t>439: source value from VISIT - SERVICE CATEGORY (#9000010-.07)</t>
-  </si>
-  <si>
     <t>Encounter.serviceType.coding.display</t>
   </si>
   <si>
@@ -1359,13 +1359,13 @@
     <t>DR.1</t>
   </si>
   <si>
+    <t>443: source value from VISIT - VISIT/ADMIT DATE&amp;TIME (#9000010-.01)</t>
+  </si>
+  <si>
     <t>Outpat.Visit.VisitDateTime
 Outpat.Workload.VisitDateTime</t>
   </si>
   <si>
-    <t>443: source value from VISIT - VISIT/ADMIT DATE&amp;TIME (#9000010-.01)</t>
-  </si>
-  <si>
     <t>Encounter.period.end</t>
   </si>
   <si>
@@ -1473,11 +1473,11 @@
     <t>Encounter.reasonCode.coding.code</t>
   </si>
   <si>
+    <t>447: source value from V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (#9000010.07-.01 &gt; 80-.01)</t>
+  </si>
+  <si>
     <t>Dim.ICD10.ICD10Code
 Dim.ICD9.ICD9Code</t>
-  </si>
-  <si>
-    <t>447: source value from V POV - POV &gt; ICD DIAGNOSIS - CODE NUMBER (#9000010.07-.01 &gt; 80-.01)</t>
   </si>
   <si>
     <t>Encounter.reasonCode.coding.display</t>
@@ -2297,8 +2297,8 @@
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="191.1328125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="125.1484375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="125.1484375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8051,10 +8051,10 @@
         <v>363</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>364</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>364</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -9839,10 +9839,10 @@
         <v>443</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>232</v>
+        <v>444</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>444</v>
+        <v>233</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -12121,10 +12121,10 @@
         <v>493</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>82</v>
+        <v>494</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -14621,10 +14621,10 @@
         <v>590</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
     </row>
     <row r="104" hidden="true">
@@ -15097,10 +15097,10 @@
         <v>613</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
     </row>
     <row r="108" hidden="true">

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4122" uniqueCount="623">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -886,6 +886,9 @@
     <t>PV1-4 / PV1-18</t>
   </si>
   <si>
+    <t>1615: source value from V CPT - CPT &gt; CPT (#9000010.18-.01 &gt; 81-)</t>
+  </si>
+  <si>
     <t>Encounter.serviceType</t>
   </si>
   <si>
@@ -1281,6 +1284,9 @@
     <t>ROL-4</t>
   </si>
   <si>
+    <t>1614: reference from V PROVIDER - PROVIDER &gt; NEW PERSON (#9000010.06-.01 &gt; 200-)</t>
+  </si>
+  <si>
     <t>Encounter.appointment</t>
   </si>
   <si>
@@ -1544,9 +1550,6 @@
   </si>
   <si>
     <t>Resources that would commonly referenced at Encounter.indication would be Condition and/or Procedure. These most closely align with DG1/PRB and PR1 respectively.</t>
-  </si>
-  <si>
-    <t>452: reference from V POV - PROBLEM LIST ENTRY (#9000010.07-.16)</t>
   </si>
   <si>
     <t>Encounter.diagnosis.use</t>
@@ -6371,7 +6374,7 @@
         <v>279</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>280</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6379,10 +6382,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6408,10 +6411,10 @@
         <v>178</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6438,13 +6441,13 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
@@ -6462,7 +6465,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6486,7 +6489,7 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6497,10 +6500,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6615,10 +6618,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6735,10 +6738,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6764,16 +6767,16 @@
         <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6822,7 +6825,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6840,13 +6843,13 @@
         <v>82</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6857,10 +6860,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6975,10 +6978,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7095,10 +7098,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7124,16 +7127,16 @@
         <v>104</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7182,7 +7185,7 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7200,13 +7203,13 @@
         <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7217,10 +7220,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7246,13 +7249,13 @@
         <v>156</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7302,7 +7305,7 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7320,13 +7323,13 @@
         <v>82</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7337,10 +7340,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7366,14 +7369,14 @@
         <v>110</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7422,7 +7425,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7440,27 +7443,27 @@
         <v>82</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7486,14 +7489,14 @@
         <v>156</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7542,7 +7545,7 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7560,13 +7563,13 @@
         <v>82</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7577,10 +7580,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7603,19 +7606,19 @@
         <v>91</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7664,7 +7667,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7682,13 +7685,13 @@
         <v>82</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7699,10 +7702,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7728,16 +7731,16 @@
         <v>156</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -7786,7 +7789,7 @@
         <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7804,13 +7807,13 @@
         <v>82</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7821,10 +7824,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7850,10 +7853,10 @@
         <v>178</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7880,13 +7883,13 @@
         <v>82</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>82</v>
@@ -7904,7 +7907,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7922,13 +7925,13 @@
         <v>82</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7939,14 +7942,14 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7965,16 +7968,16 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8024,7 +8027,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8039,19 +8042,19 @@
         <v>102</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -8059,10 +8062,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8085,13 +8088,13 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8142,7 +8145,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8157,16 +8160,16 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>160</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8177,14 +8180,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8203,13 +8206,13 @@
         <v>82</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -8260,7 +8263,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8275,10 +8278,10 @@
         <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>82</v>
@@ -8295,10 +8298,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8324,10 +8327,10 @@
         <v>235</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8378,7 +8381,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8393,16 +8396,16 @@
         <v>102</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8413,10 +8416,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8531,10 +8534,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8651,10 +8654,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8773,10 +8776,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8802,13 +8805,13 @@
         <v>178</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8837,10 +8840,10 @@
         <v>183</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8858,7 +8861,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8873,16 +8876,16 @@
         <v>102</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8893,10 +8896,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8922,10 +8925,10 @@
         <v>208</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8976,7 +8979,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8994,13 +8997,13 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
@@ -9011,10 +9014,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9037,13 +9040,13 @@
         <v>91</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9094,7 +9097,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9109,19 +9112,19 @@
         <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9129,10 +9132,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9155,13 +9158,13 @@
         <v>91</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9212,7 +9215,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9227,16 +9230,16 @@
         <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
@@ -9247,10 +9250,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9276,13 +9279,13 @@
         <v>208</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9332,7 +9335,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9347,16 +9350,16 @@
         <v>102</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9367,10 +9370,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9485,10 +9488,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9605,10 +9608,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9631,16 +9634,16 @@
         <v>91</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9690,7 +9693,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9699,7 +9702,7 @@
         <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>102</v>
@@ -9708,27 +9711,27 @@
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9751,23 +9754,23 @@
         <v>91</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>82</v>
@@ -9812,7 +9815,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9821,7 +9824,7 @@
         <v>90</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>102</v>
@@ -9830,16 +9833,16 @@
         <v>82</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>233</v>
@@ -9847,10 +9850,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9873,16 +9876,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9932,7 +9935,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9947,16 +9950,16 @@
         <v>102</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -9967,14 +9970,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -9996,13 +9999,13 @@
         <v>178</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10031,10 +10034,10 @@
         <v>114</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10052,7 +10055,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10067,16 +10070,16 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10087,10 +10090,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10205,10 +10208,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10325,10 +10328,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10354,16 +10357,16 @@
         <v>251</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10412,7 +10415,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10430,13 +10433,13 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10447,10 +10450,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10565,10 +10568,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10685,10 +10688,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10714,16 +10717,16 @@
         <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10772,7 +10775,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10790,13 +10793,13 @@
         <v>82</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10807,10 +10810,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10836,13 +10839,13 @@
         <v>156</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10892,7 +10895,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10910,13 +10913,13 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10927,10 +10930,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10956,14 +10959,14 @@
         <v>110</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11012,7 +11015,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11030,27 +11033,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11076,14 +11079,14 @@
         <v>156</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11132,7 +11135,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11150,13 +11153,13 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11167,10 +11170,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11193,19 +11196,19 @@
         <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11254,7 +11257,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11272,13 +11275,13 @@
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11289,10 +11292,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11318,16 +11321,16 @@
         <v>156</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11376,7 +11379,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11394,13 +11397,13 @@
         <v>82</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11411,14 +11414,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11437,16 +11440,16 @@
         <v>91</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11496,7 +11499,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11511,16 +11514,16 @@
         <v>102</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11531,10 +11534,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11560,10 +11563,10 @@
         <v>235</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11614,7 +11617,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11632,7 +11635,7 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>82</v>
@@ -11649,10 +11652,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11767,10 +11770,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11887,10 +11890,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12009,14 +12012,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12035,16 +12038,16 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12094,7 +12097,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>90</v>
@@ -12109,19 +12112,19 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>494</v>
+        <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>82</v>
@@ -12129,10 +12132,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12158,10 +12161,10 @@
         <v>178</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12191,10 +12194,10 @@
         <v>114</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12212,7 +12215,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12247,10 +12250,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12273,13 +12276,13 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12330,7 +12333,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12348,7 +12351,7 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
@@ -12365,10 +12368,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12391,16 +12394,16 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12450,7 +12453,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12468,7 +12471,7 @@
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>82</v>
@@ -12485,10 +12488,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12514,13 +12517,13 @@
         <v>235</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12570,7 +12573,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12588,7 +12591,7 @@
         <v>82</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
@@ -12605,10 +12608,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12723,10 +12726,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12843,10 +12846,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12965,10 +12968,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12994,10 +12997,10 @@
         <v>148</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13048,7 +13051,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13072,7 +13075,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13083,10 +13086,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13109,13 +13112,13 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -13166,7 +13169,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13184,7 +13187,7 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>82</v>
@@ -13201,10 +13204,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13230,10 +13233,10 @@
         <v>178</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13263,10 +13266,10 @@
         <v>114</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13284,7 +13287,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13302,13 +13305,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13319,10 +13322,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13348,10 +13351,10 @@
         <v>178</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13378,13 +13381,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13402,7 +13405,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13426,7 +13429,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13437,10 +13440,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13466,16 +13469,16 @@
         <v>178</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13500,13 +13503,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13524,7 +13527,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13542,13 +13545,13 @@
         <v>82</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13559,10 +13562,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13588,10 +13591,10 @@
         <v>178</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13621,10 +13624,10 @@
         <v>114</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13642,7 +13645,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13660,13 +13663,13 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13677,10 +13680,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13706,10 +13709,10 @@
         <v>178</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13739,10 +13742,10 @@
         <v>114</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>82</v>
@@ -13760,7 +13763,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -13778,13 +13781,13 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13795,10 +13798,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13821,13 +13824,13 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13878,7 +13881,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -13896,13 +13899,13 @@
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -13913,10 +13916,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13942,10 +13945,10 @@
         <v>178</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13975,10 +13978,10 @@
         <v>114</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -13996,7 +13999,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14014,13 +14017,13 @@
         <v>82</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14031,10 +14034,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14060,13 +14063,13 @@
         <v>235</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14116,7 +14119,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14134,7 +14137,7 @@
         <v>82</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>82</v>
@@ -14151,10 +14154,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14269,10 +14272,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14389,10 +14392,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14511,10 +14514,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14537,13 +14540,13 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -14594,7 +14597,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>90</v>
@@ -14609,19 +14612,19 @@
         <v>102</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>82</v>
@@ -14629,10 +14632,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14658,13 +14661,13 @@
         <v>110</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -14693,10 +14696,10 @@
         <v>172</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14714,7 +14717,7 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
@@ -14732,7 +14735,7 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>82</v>
@@ -14749,10 +14752,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14778,13 +14781,13 @@
         <v>178</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14810,13 +14813,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -14834,7 +14837,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14869,10 +14872,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14898,10 +14901,10 @@
         <v>208</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14952,7 +14955,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -14970,7 +14973,7 @@
         <v>82</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>82</v>
@@ -14987,10 +14990,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15013,13 +15016,13 @@
         <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15070,7 +15073,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15085,19 +15088,19 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>82</v>
@@ -15105,10 +15108,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15131,16 +15134,16 @@
         <v>82</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15190,7 +15193,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15205,10 +15208,10 @@
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>82</v>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
+++ b/docs/StructureDefinition-EncounterOutpatientVisit.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
